--- a/Equifax_Test_Report.xlsx
+++ b/Equifax_Test_Report.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,13 +25,35 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00BDD7EE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E5F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0092D050"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +68,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,130 +440,105 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E106"/>
+  <dimension ref="A1:G178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>SCN_001 &gt;&gt; Verify Data Provider Report Changes to Include OneScore and Remove CIDS Score</t>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Test Summary: Testing mSupply</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Test Case ID</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Step</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Tester: Bhargav Balla</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>Reviewed By: Harish Arunachalam</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>EQFX_001 &gt;&gt; Verify Data Provider Report Changes - Add OneScore Package SCR2038</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>TestCase ID</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Test Steps</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>TC_001_01</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Login to application</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>User should be able to login successfully</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>TC_001_02</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Navigate to Data Provider settings module</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Data Provider settings page should be displayed</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>TC_001_03</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Verify Product Option Package SCR2038 is added to the configuration list</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>SCR2038 (Equifax OneScore for CTFS) should be visible in the configuration</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>TC_001_04</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Verify all CIDS related entries are removed from Data Provider settings</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>No CIDS related entries should be present in the configuration</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Test Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>TC_001</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Login to Salesforce with Credit Analyst credentials</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>User successfully logs into Salesforce</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>TC_001</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Navigate to Data Provider settings for Equifax</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Data Provider configuration page is displayed</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -545,51 +547,63 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SCN_002 &gt;&gt; Verify OneScore field is added on Account, Decision, and Equifax Blended Object</t>
+          <t>TC_001</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Verify Product Option Package SCR2038 is added to configuration</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>SCR2038 (Equifax OneScore for CTFS) is visible in Product Option Package list</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Test Case ID</t>
+          <t>TC_001</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Step</t>
+          <t>Verify all CIDS (SCR0117) related entries are removed</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Expected Result</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Actual Result</t>
-        </is>
-      </c>
+          <t>No CIDS related entries or mapping logic present in Data Provider settings</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TC_002_01</t>
+          <t>TC_001</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Login to application</t>
+          <t>Pull credit report and verify OneScore is populated in Account</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>User should be able to login successfully</t>
+          <t>OneScore value is successfully populated after credit pull</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -599,70 +613,58 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>TC_002_02</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Navigate to Account object under Relationship Information section</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Account object page should be displayed</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>TC_002_03</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Verify OneScore field is visible and readonly for Credit Analyst and System Admin</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>OneScore field should be visible and readonly on Account, Decision, and Equifax Blended objects</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>TC_002_04</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Verify OneScore field displays N/A when no score is generated</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Field should remain blank or display N/A when no OneScore exists</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>EQFX_002 &gt;&gt; Verify OneScore field addition on Account object</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>TestCase ID</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Test Steps</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Test Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>TC_002</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Login to Salesforce with Credit Analyst credentials</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>User successfully logs into Salesforce</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -671,51 +673,63 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SCN_003 &gt;&gt; Verify Scorecard Type field is added on Account, Decision, and Equifax Blended Object</t>
+          <t>TC_002</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Navigate to Account object under Relationship Information section</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Account page is displayed with Relationship Information section</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Test Case ID</t>
+          <t>TC_002</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Step</t>
+          <t>Verify OneScore field is visible and Read-Only</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Expected Result</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Actual Result</t>
-        </is>
-      </c>
+          <t>OneScore field is displayed and cannot be edited</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>TC_003_01</t>
+          <t>TC_002</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Login to application</t>
+          <t>Verify field displays N/A when no score is generated</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>User should be able to login successfully</t>
+          <t>Field shows blank or N/A when OneScore has not been generated</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -725,70 +739,58 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>TC_003_02</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Navigate to Account object under Relationship Information section</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Account object page should be displayed</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>TC_003_03</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Verify Scorecard Type field is visible and readonly for all users</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Scorecard Type field should be visible and readonly on all mentioned objects</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>TC_003_04</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Verify Scorecard Type populates correct values based on credit hits</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Field should display Commercial, Consumer, or Blended based on credit report data</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>EQFX_003 &gt;&gt; Verify OneScore field addition on Decision object</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>TestCase ID</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Test Steps</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Test Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>TC_003</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Login to Salesforce with Credit Analyst credentials</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>User successfully logs into Salesforce</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -797,51 +799,63 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SCN_004 &gt;&gt; Verify new Scorecard Calculation Decision OneScore</t>
+          <t>TC_003</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Navigate to Decision object under Score Card Information section</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Decision page is displayed with Score Card Information section</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Test Case ID</t>
+          <t>TC_003</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Step</t>
+          <t>Verify OneScore field is visible and Read-Only</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Expected Result</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Actual Result</t>
-        </is>
-      </c>
+          <t>OneScore field is displayed and cannot be edited</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>TC_004_01</t>
+          <t>TC_003</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Login to application</t>
+          <t>Perform credit pull and verify OneScore population</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>User should be able to login successfully</t>
+          <t>OneScore value is populated correctly after credit pull</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -851,70 +865,58 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>TC_004_02</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Navigate to Decision scorecard module</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Decision scorecard page should be displayed</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>TC_004_03</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Verify WEF Score Credit Rating and WEF Risk Rating are populated based on OneScore ranges</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Rating fields should be auto-populated based on defined OneScore ranges</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>TC_004_04</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Verify Primary Decision is populated based on OneScore and CutoffSegment values</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Primary Decision should show Approve, Rec Approve, or Rec Decline based on scoring logic</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>EQFX_004 &gt;&gt; Verify OneScore field addition on Equifax Blended Object</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>TestCase ID</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>Test Steps</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>Test Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>TC_004</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Login to Salesforce with Credit Analyst credentials</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>User successfully logs into Salesforce</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -923,51 +925,63 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SCN_005 &gt;&gt; Verify Fraud Victim Alert Indicator field on Decision and Equifax Consumer Object</t>
+          <t>TC_004</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Navigate to Equifax Blended Object under Credit Information section</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Equifax Blended Object page is displayed</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Test Case ID</t>
+          <t>TC_004</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Step</t>
+          <t>Verify OneScore field is visible and Read-Only</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Expected Result</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Actual Result</t>
-        </is>
-      </c>
+          <t>OneScore field is displayed and cannot be edited</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>TC_005_01</t>
+          <t>TC_004</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Login to application</t>
+          <t>Verify OneScore displays commercial, consumer or blended score</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>User should be able to login successfully</t>
+          <t>OneScore shows appropriate value based on scorecard type</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -977,70 +991,58 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>TC_005_02</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Navigate to Decision object under Viewed Variables section</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Decision object page should be displayed</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>TC_005_03</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Verify Fraud Victim Alert Indicator field is visible and readonly</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Field should be visible under Viewed Variables section and readonly</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>TC_005_04</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Verify field populates correct fraud alert codes from credit report</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Field should display correct codes like N, Q, R, T, V, W, X based on report data</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>EQFX_005 &gt;&gt; Verify Scorecard Type field addition on Account object</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>TestCase ID</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>Test Steps</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>Test Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>TC_005</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Login to Salesforce with Credit Analyst credentials</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>User successfully logs into Salesforce</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -1049,51 +1051,63 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SCN_006 &gt;&gt; Verify PG Active Duty and PG Fraud Victim fields on Decision and Equifax Consumer Object</t>
+          <t>TC_005</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Navigate to Account object under Relationship Information section</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Account page is displayed with Relationship Information section</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Test Case ID</t>
+          <t>TC_005</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Step</t>
+          <t>Verify Scorecard Type field is visible and Read-Only</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Expected Result</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Actual Result</t>
-        </is>
-      </c>
+          <t>Scorecard Type field is displayed and cannot be edited</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>TC_006_01</t>
+          <t>TC_005</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Login to application</t>
+          <t>Verify field populates correct values - Commercial only, Consumer, or Blended</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>User should be able to login successfully</t>
+          <t>Scorecard Type shows correct value based on credit hit type</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
@@ -1103,70 +1117,58 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>TC_006_02</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Navigate to Decision object under Viewed Variables section</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Decision object page should be displayed</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>TC_006_03</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Verify PG Active Duty and PG Fraud Victim checkbox fields are visible and readonly</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Both checkbox fields should be present and readonly on specified objects</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>TC_006_04</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Verify checkboxes are enabled when alerts are present in credit report</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Checkboxes should be enabled when respective alerts are found in report</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>EQFX_006 &gt;&gt; Verify Scorecard Type field addition on Decision object</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>TestCase ID</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>Test Steps</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>Test Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>TC_006</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Login to Salesforce with Credit Analyst credentials</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>User successfully logs into Salesforce</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -1175,51 +1177,63 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SCN_007 &gt;&gt; Verify Prescoring Rule for Fraud and Active Duty Alerts</t>
+          <t>TC_006</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Navigate to Decision object under Score Card Information section</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Decision page is displayed with Score Card Information section</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Test Case ID</t>
+          <t>TC_006</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Step</t>
+          <t>Verify Scorecard Type field is visible and Read-Only for all users</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Expected Result</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Actual Result</t>
-        </is>
-      </c>
+          <t>Scorecard Type field is displayed and cannot be edited</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>TC_007_01</t>
+          <t>TC_006</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Login to application</t>
+          <t>Perform credit pull with commercial hit only and verify value</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>User should be able to login successfully</t>
+          <t>Scorecard Type displays 'Commercial only'</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
@@ -1229,70 +1243,58 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>TC_007_02</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Navigate to prescoring rules module</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Prescoring rules page should be displayed</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>TC_007_03</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Verify Secondary Decision is set to Manual Review when Fraud Victim Alert is present</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Secondary Decision should be Manual Review if fraud alert exists</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>TC_007_04</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Verify Secondary Decision is set to Manual Review when Active Duty Alert is present</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Secondary Decision should be Manual Review if active duty alert exists</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>EQFX_007 &gt;&gt; Verify Scorecard Type field addition on Equifax Blended Object</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>TestCase ID</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>Test Steps</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>Test Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>TC_007</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Login to Salesforce with Credit Analyst credentials</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>User successfully logs into Salesforce</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -1301,51 +1303,63 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SCN_008 &gt;&gt; Verify Rule 11 Exceeds App Only limit for Manual Review</t>
+          <t>TC_007</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Navigate to Equifax Blended Object under Credit Information section</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Equifax Blended Object page is displayed</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Test Case ID</t>
+          <t>TC_007</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Step</t>
+          <t>Verify Scorecard Type field populates based on hit type</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Expected Result</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>Actual Result</t>
-        </is>
-      </c>
+          <t>Field shows Commercial, Consumer, or Blended based on credit report data</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>TC_008_01</t>
+          <t>TC_007</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Login to application</t>
+          <t>Verify average calculation when multiple PGs with Consumer hit</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>User should be able to login successfully</t>
+          <t>When Scorecard Type is Consumer with multiple PGs, average OneScore is displayed</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
@@ -1355,100 +1369,100 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>TC_008_02</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Navigate to post scoring rules module</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Post scoring rules page should be displayed</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>TC_008_03</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Verify PostScoreAction is set to Manual Review when Primary Decision is Approve and Aggregate Exposure exceeds $500,000</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>PostScoreAction should trigger Manual Review for approvals exceeding $500K</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>Pass</t>
+    <row r="62">
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>EQFX_008 &gt;&gt; Verify new Decision OneScore Scorecard calculation</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>TestCase ID</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>Test Steps</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>Test Status</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>SCN_009 &gt;&gt; Verify Rule 22 Exceeds Comparable Credit for Manual Review</t>
+          <t>TC_008</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Login to Salesforce with Credit Analyst credentials</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>User successfully logs into Salesforce</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Test Case ID</t>
+          <t>TC_008</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Step</t>
+          <t>Navigate to Scorecard configuration section</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Expected Result</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>Actual Result</t>
-        </is>
-      </c>
+          <t>Scorecard configuration page is displayed</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>TC_009_01</t>
+          <t>TC_008</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Login to application</t>
+          <t>Verify Decision OneScore scorecard is active when prescoring rules are enabled</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>User should be able to login successfully</t>
+          <t>Decision OneScore scorecard is in execution mode</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
@@ -1461,17 +1475,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>TC_009_02</t>
+          <t>TC_008</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Navigate to post scoring rules module</t>
+          <t>Verify WEF Score Credit Rating and WEF Risk Rating are populated based on OneScore ranges</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Post scoring rules page should be displayed</t>
+          <t>WEF Score Credit Rating and WEF Risk Rating fields are correctly populated</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
@@ -1484,17 +1498,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>TC_009_03</t>
+          <t>TC_008</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Verify PostScoreAction is set to Manual Review when Total Finance Amount exceeds $350,000 and high credit is less than 50% of equipment cost</t>
+          <t>Verify Primary Decision is populated based on OneScore and CutoffSegment values</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>PostScoreAction should be Manual Review when conditions are met</t>
+          <t>Primary Decision shows Approve, Rec Approve, or Rec Decline based on defined ranges</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
@@ -1505,53 +1519,53 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>SCN_010 &gt;&gt; Verify Rule 23 Exceeds OneScore Consumer Only for Manual Review</t>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>EQFX_009 &gt;&gt; Verify Fraud Victim Alert Indicator field on Decision object</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Test Case ID</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Step</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>TestCase ID</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>Test Steps</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
+      <c r="D72" s="3" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>Status</t>
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>Test Status</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>TC_010_01</t>
+          <t>TC_009</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Login to application</t>
+          <t>Login to Salesforce with Credit Analyst credentials</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>User should be able to login successfully</t>
+          <t>User successfully logs into Salesforce</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
@@ -1564,17 +1578,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>TC_010_02</t>
+          <t>TC_009</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Navigate to post scoring rules module</t>
+          <t>Navigate to Decision object under Viewed Variables section</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Post scoring rules page should be displayed</t>
+          <t>Decision page with Viewed Variables section is displayed</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
@@ -1587,17 +1601,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>TC_010_03</t>
+          <t>TC_009</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Verify PostScoreAction is set to Manual Review when Primary Decision is Approve and ScoreType is Consumer Only</t>
+          <t>Verify Fraud Victim Alert Indicator field is visible and Read-Only</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>PostScoreAction should be Manual Review when approval is based solely on consumer data</t>
+          <t>Fraud Victim Alert Indicator field is displayed and cannot be edited</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
@@ -1607,77 +1621,77 @@
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>SCN_011 &gt;&gt; Verify Post Scoring Rules related to CIDS are removed</t>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>TC_009</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Submit application with PG having Fraud Victim Alert and verify value population</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Fraud Victim Alert Indicator is populated with correct code (N, Q, R, T, V, W, or X)</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Test Case ID</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Step</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>EQFX_010 &gt;&gt; Verify Fraud Victim Alert Indicator field on Equifax Consumer Object</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>TestCase ID</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>Test Steps</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
+      <c r="D80" s="3" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>TC_011_01</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Login to application</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>User should be able to login successfully</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr"/>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="E80" s="3" t="inlineStr">
+        <is>
+          <t>Test Status</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>TC_011_02</t>
+          <t>TC_010</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Navigate to post scoring rules module</t>
+          <t>Login to Salesforce with Credit Analyst credentials</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Post scoring rules page should be displayed</t>
+          <t>User successfully logs into Salesforce</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
@@ -1690,17 +1704,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>TC_011_03</t>
+          <t>TC_010</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Verify CIDS rules 17 and 19 are no longer present in the scoring engine</t>
+          <t>Navigate to Equifax Consumer Object under Consumer Information section</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>CIDS related rules should be completely removed from the system</t>
+          <t>Equifax Consumer Object page is displayed</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
@@ -1713,17 +1727,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>TC_011_04</t>
+          <t>TC_010</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Verify system does not check for CIDS values or missing CIDS data</t>
+          <t>Verify Fraud Victim Alert Indicator field is visible and Read-Only</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>No CIDS triggers should be active for Manual Review decisions</t>
+          <t>Field is displayed and cannot be edited by user</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
@@ -1733,77 +1747,77 @@
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>SCN_012 &gt;&gt; Verify Exceeds Comparable Limit field on Decision and Equifax Blended Object</t>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>TC_010</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Verify field populates values directly from credit report</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Fraud Victim Alert Indicator shows correct value from consumer credit report</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Test Case ID</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Step</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>EQFX_011 &gt;&gt; Verify PG Active Duty and PG Fraud Victim fields on Decision object</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="3" t="inlineStr">
+        <is>
+          <t>TestCase ID</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>Test Steps</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr">
+      <c r="D88" s="3" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>TC_012_01</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Login to application</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>User should be able to login successfully</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr"/>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="E88" s="3" t="inlineStr">
+        <is>
+          <t>Test Status</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>TC_012_02</t>
+          <t>TC_011</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Navigate to Decision object under Viewed Variables section</t>
+          <t>Login to Salesforce with Credit Analyst credentials</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Decision object page should be displayed</t>
+          <t>User successfully logs into Salesforce</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
@@ -1816,17 +1830,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>TC_012_03</t>
+          <t>TC_011</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Verify Exceeds Comparable Limit checkbox field is visible and readonly</t>
+          <t>Navigate to Decision object under Viewed Variables section</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Field should be present and readonly on specified objects</t>
+          <t>Decision page with Viewed Variables section is displayed</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
@@ -1839,17 +1853,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>TC_012_04</t>
+          <t>TC_011</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Verify checkbox is enabled when Rule 22 conditions are satisfied</t>
+          <t>Verify PG Active Duty and PG Fraud Victim checkbox fields are present and Read-Only</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Checkbox should be enabled when Rule 22 criteria are met</t>
+          <t>Both checkbox fields are visible and cannot be edited</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
@@ -1859,77 +1873,77 @@
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>SCN_013 &gt;&gt; Verify OneScore and Scorecard Type fields are removed from Equifax Commercial Object</t>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>TC_011</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Submit application with alerts and verify checkboxes are enabled appropriately</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Checkboxes are enabled when corresponding alerts are present in credit report</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Test Case ID</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Step</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>EQFX_012 &gt;&gt; Verify PG Active Duty and PG Fraud Victim fields on Equifax Consumer Object</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="inlineStr">
+        <is>
+          <t>TestCase ID</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>Test Steps</t>
+        </is>
+      </c>
+      <c r="C96" s="3" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr">
+      <c r="D96" s="3" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>TC_013_01</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Login to application</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>User should be able to login successfully</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr"/>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="E96" s="3" t="inlineStr">
+        <is>
+          <t>Test Status</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>TC_013_02</t>
+          <t>TC_012</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Navigate to Equifax Commercial Object</t>
+          <t>Login to Salesforce with Credit Analyst credentials</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Equifax Commercial Object page should be displayed</t>
+          <t>User successfully logs into Salesforce</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
@@ -1942,17 +1956,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>TC_013_03</t>
+          <t>TC_012</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Verify OneScore field is not visible under Equifax Commercial Object</t>
+          <t>Navigate to Equifax Consumer Object under Consumer Information section</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>OneScore field should not be present on Equifax Commercial Object</t>
+          <t>Equifax Consumer Object page is displayed</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
@@ -1965,17 +1979,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>TC_013_04</t>
+          <t>TC_012</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Verify Scorecard Type field is not visible under Equifax Commercial Object</t>
+          <t>Verify PG Active Duty and PG Fraud Victim fields are present</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Scorecard Type field should not be present on Equifax Commercial Object</t>
+          <t>Both checkbox fields are visible on the object</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
@@ -1985,77 +1999,77 @@
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>SCN_014 &gt;&gt; Verify Decision Screen UI Improvements with CIDS fields removed</t>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>TC_012</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Verify values are populated from credit report</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Fields are correctly populated based on consumer credit report data</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Test Case ID</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Step</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>EQFX_013 &gt;&gt; Verify Prescoring Rule - PG Fraud Alert sets Secondary Decision to Manual Review</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="3" t="inlineStr">
+        <is>
+          <t>TestCase ID</t>
+        </is>
+      </c>
+      <c r="B104" s="3" t="inlineStr">
+        <is>
+          <t>Test Steps</t>
+        </is>
+      </c>
+      <c r="C104" s="3" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr">
+      <c r="D104" s="3" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>TC_014_01</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Login to application</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>User should be able to login successfully</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr"/>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="E104" s="3" t="inlineStr">
+        <is>
+          <t>Test Status</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>TC_014_02</t>
+          <t>TC_013</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Navigate to Decision object</t>
+          <t>Login to Salesforce with Credit Analyst credentials</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Decision object page should be displayed</t>
+          <t>User successfully logs into Salesforce</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
@@ -2068,17 +2082,17 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>TC_014_03</t>
+          <t>TC_013</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Verify all CIDS related fields are not visible on Decision object</t>
+          <t>Navigate to Application with Personal Guarantor</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>No CIDS or CIDS Rate fields should be present on Decision screen</t>
+          <t>Application page is displayed</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
@@ -2088,7 +2102,1222 @@
         </is>
       </c>
     </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>TC_013</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Pull Consumer BPR Report for PG with Fraud Victim Alert</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Credit report is pulled successfully showing Fraud Victim Alert</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>TC_013</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Verify Secondary Decision is set to Manual Review</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Secondary Decision automatically set to Manual Review</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>TC_013</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Verify PG Fraud Victim checkbox is enabled</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>PG Fraud Victim checkbox is checked</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>EQFX_014 &gt;&gt; Verify Prescoring Rule - PG Active Duty Alert sets Secondary Decision to Manual Review</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="3" t="inlineStr">
+        <is>
+          <t>TestCase ID</t>
+        </is>
+      </c>
+      <c r="B113" s="3" t="inlineStr">
+        <is>
+          <t>Test Steps</t>
+        </is>
+      </c>
+      <c r="C113" s="3" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="D113" s="3" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="E113" s="3" t="inlineStr">
+        <is>
+          <t>Test Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>TC_014</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Login to Salesforce with Credit Analyst credentials</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>User successfully logs into Salesforce</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>TC_014</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Navigate to Application with Personal Guarantor</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Application page is displayed</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>TC_014</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Pull Consumer BPR Report for PG with Active Duty Alert</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Credit report is pulled successfully showing Active Duty Alert</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>TC_014</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Verify Secondary Decision is set to Manual Review</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Secondary Decision automatically set to Manual Review</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>TC_014</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Verify PG Active Duty checkbox is enabled</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>PG Active Duty checkbox is checked</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr"/>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>EQFX_015 &gt;&gt; Verify Post-Scoring Rule 11 - Exceeds App Only Limit ($500K)</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="3" t="inlineStr">
+        <is>
+          <t>TestCase ID</t>
+        </is>
+      </c>
+      <c r="B122" s="3" t="inlineStr">
+        <is>
+          <t>Test Steps</t>
+        </is>
+      </c>
+      <c r="C122" s="3" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="D122" s="3" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="E122" s="3" t="inlineStr">
+        <is>
+          <t>Test Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>TC_015</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Login to Salesforce with Credit Analyst credentials</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>User successfully logs into Salesforce</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr"/>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>TC_015</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Navigate to Application with Primary Decision as Approve</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Application page is displayed with Decision details</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>TC_015</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Set Aggregate Exposure greater than $500,000</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Aggregate Exposure value is set above $500K threshold</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr"/>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>TC_015</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Execute post-scoring rules</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Post-scoring rules are executed successfully</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr"/>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>TC_015</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Verify PostScoreAction is set to Manual Review</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>PostScoreAction is automatically set to Manual Review</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr"/>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>EQFX_016 &gt;&gt; Verify Post-Scoring Rule 22 - Exceeds Comparable Credit ($350K)</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="3" t="inlineStr">
+        <is>
+          <t>TestCase ID</t>
+        </is>
+      </c>
+      <c r="B131" s="3" t="inlineStr">
+        <is>
+          <t>Test Steps</t>
+        </is>
+      </c>
+      <c r="C131" s="3" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="D131" s="3" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="E131" s="3" t="inlineStr">
+        <is>
+          <t>Test Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>TC_016</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Login to Salesforce with Credit Analyst credentials</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>User successfully logs into Salesforce</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr"/>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>TC_016</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Navigate to Opportunity with Total Finance Amount greater than $350,000</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Opportunity page is displayed</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr"/>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>TC_016</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Set Primary Decision to Approve and Single High Credit less than 50% of Equipment Cost</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Conditions for Rule 22 are met</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr"/>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>TC_016</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Execute post-scoring rules</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Post-scoring rules are executed successfully</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr"/>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>TC_016</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Verify PostScoreAction is set to Manual Review and Exceeds Comparable Limit checkbox is enabled</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>PostScoreAction is set to Manual Review and checkbox is checked</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr"/>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>EQFX_017 &gt;&gt; Verify Post-Scoring Rule 23 - Exceeds OneScore Consumer Only</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="3" t="inlineStr">
+        <is>
+          <t>TestCase ID</t>
+        </is>
+      </c>
+      <c r="B140" s="3" t="inlineStr">
+        <is>
+          <t>Test Steps</t>
+        </is>
+      </c>
+      <c r="C140" s="3" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="D140" s="3" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="E140" s="3" t="inlineStr">
+        <is>
+          <t>Test Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>TC_017</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Login to Salesforce with Credit Analyst credentials</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>User successfully logs into Salesforce</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr"/>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>TC_017</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Navigate to Decision with Primary Decision as Approve</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Decision page is displayed</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr"/>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>TC_017</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Set ScoreType to Consumer Only (No Commercial Data)</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>ScoreType is set to Consumer Only</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr"/>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>TC_017</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Execute post-scoring rules</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Post-scoring rules are executed successfully</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr"/>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>TC_017</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Verify PostScoreAction is set to Manual Review</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>PostScoreAction is automatically set to Manual Review for consumer-only approvals</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr"/>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>EQFX_018 &gt;&gt; Verify Removal of CIDS Post-Scoring Rules (Rule 17 &amp; 19)</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="3" t="inlineStr">
+        <is>
+          <t>TestCase ID</t>
+        </is>
+      </c>
+      <c r="B149" s="3" t="inlineStr">
+        <is>
+          <t>Test Steps</t>
+        </is>
+      </c>
+      <c r="C149" s="3" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="D149" s="3" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="E149" s="3" t="inlineStr">
+        <is>
+          <t>Test Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>TC_018</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Login to Salesforce with System Admin credentials</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>User successfully logs into Salesforce</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr"/>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>TC_018</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Navigate to Scoring Engine configuration</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Scoring Engine configuration page is displayed</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr"/>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>TC_018</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Verify CIDS &lt; 470 rule is removed from post-scoring</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>No rule exists checking CIDS &lt; 470 for Manual Review trigger</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr"/>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>TC_018</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Verify missing CIDS and MSv2 rule is removed</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>No rule exists checking for missing CIDS data</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr"/>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>TC_018</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Process application and verify no CIDS-based Manual Review triggers</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>System does not trigger Manual Review based on CIDS values</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr"/>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>EQFX_019 &gt;&gt; Verify Exceeds Comparable Limit checkbox field on Decision object</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="3" t="inlineStr">
+        <is>
+          <t>TestCase ID</t>
+        </is>
+      </c>
+      <c r="B158" s="3" t="inlineStr">
+        <is>
+          <t>Test Steps</t>
+        </is>
+      </c>
+      <c r="C158" s="3" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="D158" s="3" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="E158" s="3" t="inlineStr">
+        <is>
+          <t>Test Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>TC_019</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Login to Salesforce with Credit Analyst credentials</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>User successfully logs into Salesforce</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr"/>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>TC_019</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Navigate to Decision object under Viewed Variables section</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Decision page with Viewed Variables section is displayed</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr"/>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>TC_019</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Verify Exceeds Comparable Limit checkbox field is present and Read-Only</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Exceeds Comparable Limit checkbox is visible and cannot be edited</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr"/>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>TC_019</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Trigger Rule 22 conditions and verify checkbox is enabled</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Checkbox is checked when Rule 22 conditions are satisfied</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr"/>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>EQFX_020 &gt;&gt; Verify Exceeds Comparable Limit checkbox field on Equifax Blended Object</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="3" t="inlineStr">
+        <is>
+          <t>TestCase ID</t>
+        </is>
+      </c>
+      <c r="B166" s="3" t="inlineStr">
+        <is>
+          <t>Test Steps</t>
+        </is>
+      </c>
+      <c r="C166" s="3" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="D166" s="3" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="E166" s="3" t="inlineStr">
+        <is>
+          <t>Test Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>TC_020</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Login to Salesforce with Credit Analyst credentials</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>User successfully logs into Salesforce</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr"/>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>TC_020</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Navigate to Equifax Blended Object under Consumer Information section</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Equifax Blended Object page is displayed</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr"/>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>TC_020</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Verify Exceeds Comparable Limit field is visible and Read-Only</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Field is displayed and cannot be edited</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr"/>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>TC_020</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Verify field is populated from report data when Rule 22 is satisfied</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Checkbox is enabled based on Rule 22 satisfaction</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr"/>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>EQFX_021 &gt;&gt; Verify Removal of OneScore and Scorecard Type fields from Equifax Commercial Object</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="3" t="inlineStr">
+        <is>
+          <t>TestCase ID</t>
+        </is>
+      </c>
+      <c r="B174" s="3" t="inlineStr">
+        <is>
+          <t>Test Steps</t>
+        </is>
+      </c>
+      <c r="C174" s="3" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="D174" s="3" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="E174" s="3" t="inlineStr">
+        <is>
+          <t>Test Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>TC_021</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Login to Salesforce with System Admin credentials</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>User successfully logs into Salesforce</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr"/>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>TC_021</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Navigate to Equifax Commercial Object</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Equifax Commercial Object page is displayed</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr"/>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>TC_021</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Verify OneScore field is not present on the object</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>OneScore field is not visible on Equifax Commercial Object</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr"/>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>TC_021</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Verify Scorecard Type field is not present on the object</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Scorecard Type field is not visible on Equifax Commercial Object</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr"/>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="21">
+    <mergeCell ref="B14:G14"/>
+    <mergeCell ref="B148:G148"/>
+    <mergeCell ref="B157:G157"/>
+    <mergeCell ref="B87:G87"/>
+    <mergeCell ref="B38:G38"/>
+    <mergeCell ref="B103:G103"/>
+    <mergeCell ref="B112:G112"/>
+    <mergeCell ref="B30:G30"/>
+    <mergeCell ref="B139:G139"/>
+    <mergeCell ref="B95:G95"/>
+    <mergeCell ref="B5:G5"/>
+    <mergeCell ref="B79:G79"/>
+    <mergeCell ref="B173:G173"/>
+    <mergeCell ref="B62:G62"/>
+    <mergeCell ref="B165:G165"/>
+    <mergeCell ref="B54:G54"/>
+    <mergeCell ref="B46:G46"/>
+    <mergeCell ref="B121:G121"/>
+    <mergeCell ref="B22:G22"/>
+    <mergeCell ref="B71:G71"/>
+    <mergeCell ref="B130:G130"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>